--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -484,10 +484,10 @@
         <v>3.48</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.03947826086956763</v>
+        <v>0.01974137931034692</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -505,10 +505,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.448012329545969</v>
+        <v>3.42868537831944</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.04801232954596824</v>
+        <v>0.02868537831944007</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -526,10 +526,10 @@
         <v>95.39999999999999</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.65217391304348</v>
+        <v>95.68965517241379</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2521739130434923</v>
+        <v>0.2896551724138021</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -547,10 +547,10 @@
         <v>4.6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.347826086956522</v>
+        <v>4.310344827586207</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2521739130434781</v>
+        <v>-0.2896551724137924</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         <v>4.06</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.983943837120484</v>
+        <v>3.972276416934467</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.076056162879516</v>
+        <v>-0.0877235830655323</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>0.86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8834156315349508</v>
+        <v>0.8810417533861374</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.02341563153495085</v>
+        <v>0.02104175338613745</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -610,10 +610,10 @@
         <v>13.96</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>14.58478488287689</v>
+        <v>14.56591488300176</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.6247848828768845</v>
+        <v>0.6059148830017609</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>88.28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>94.25806451612905</v>
+        <v>94.54147465437789</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5.978064516129052</v>
+        <v>6.261474654377892</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>3.52</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.03227060364503664</v>
+        <v>0.01464221678890887</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>-0.04</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01469001100112149</v>
+        <v>0.01331609830531429</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Table 2 - Paper vs Current.xlsx
+++ b/isolated_excel/Table 2 - Paper vs Current.xlsx
@@ -443,7 +443,7 @@
     <col width="31" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -484,10 +484,10 @@
         <v>3.48</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145301</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.01974137931034692</v>
+        <v>-0.0008547008546986312</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -505,10 +505,10 @@
         <v>3.4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3.42868537831944</v>
+        <v>3.408469136214709</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.02868537831944007</v>
+        <v>0.008469136214708683</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -526,10 +526,10 @@
         <v>95.39999999999999</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>95.68965517241379</v>
+        <v>95.72649572649573</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.2896551724138021</v>
+        <v>0.326495726495736</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -547,10 +547,10 @@
         <v>4.6</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4.310344827586207</v>
+        <v>4.273504273504273</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.2896551724137924</v>
+        <v>-0.3264957264957262</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -568,10 +568,10 @@
         <v>4.06</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3.972276416934467</v>
+        <v>3.961386811469624</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.0877235830655323</v>
+        <v>-0.0986131885303756</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -589,10 +589,10 @@
         <v>0.86</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.8810417533861374</v>
+        <v>0.8782644727023218</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.02104175338613745</v>
+        <v>0.01826447270232179</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -610,10 +610,10 @@
         <v>13.96</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>14.56591488300176</v>
+        <v>14.54247474070697</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.6059148830017609</v>
+        <v>0.5824747407069726</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -631,10 +631,10 @@
         <v>88.28</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>94.54147465437789</v>
+        <v>94.79262672811062</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6.261474654377892</v>
+        <v>6.512626728110618</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -652,10 +652,10 @@
         <v>3.52</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.01464221678890887</v>
+        <v>-0.008570680063785918</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         <v>-0.04</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0.01331609830531429</v>
+        <v>0.01504717870783059</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
